--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_143_R15.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_143_R15.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4328</v>
+        <v>6.323</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4843</v>
+        <v>6.6769</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0515</v>
+        <v>-0.354</v>
       </c>
       <c r="G2" t="n">
         <v>5.2847</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>0.148</v>
+        <v>0.0382</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0395</v>
+        <v>0.2322</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1085</v>
+        <v>-0.1939</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4955</v>
+        <v>3.0122</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5664</v>
+        <v>2.9151</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0709</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>0.6867</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8499</v>
+        <v>0.3666</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6226</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.6047</v>
       </c>
       <c r="V3" t="n">
         <v>0.5671</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5732</v>
+        <v>2.1611</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2253</v>
+        <v>3.3046</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6521</v>
+        <v>-1.1434</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9992</v>
+        <v>1.8193</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2388</v>
+        <v>0.143</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2379</v>
+        <v>1.6763</v>
       </c>
       <c r="J4" t="n">
-        <v>3.255</v>
+        <v>2.9703</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5952</v>
+        <v>0.5546</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6599</v>
+        <v>2.4157</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2559</v>
+        <v>-1.1509</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8339</v>
+        <v>-0.4116</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.422</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7481</v>
+        <v>-0.0679</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3339</v>
+        <v>0.3343</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4143</v>
+        <v>-0.4022</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3943</v>
+        <v>-1.214</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3526</v>
+        <v>1.6814</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5968</v>
+        <v>3.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2443</v>
+        <v>-1.6185</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8193</v>
+        <v>0.9992</v>
       </c>
       <c r="H5" t="n">
-        <v>0.143</v>
+        <v>-0.2388</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6763</v>
+        <v>1.2379</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9703</v>
+        <v>3.255</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5546</v>
+        <v>0.5952</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4157</v>
+        <v>2.6599</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1509</v>
+        <v>-2.2559</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4116</v>
+        <v>-0.8339</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.422</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8764</v>
+        <v>-0.6398</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3734</v>
+        <v>-0.2592</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.503</v>
+        <v>-0.3806</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.214</v>
+        <v>0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.524</v>
+        <v>0.65</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7352</v>
+        <v>1.1637</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2112</v>
+        <v>-0.5137</v>
       </c>
       <c r="G6" t="n">
         <v>0.3992</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0196</v>
+        <v>-0.8935</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8962</v>
+        <v>-0.4676</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1234</v>
+        <v>-0.4259</v>
       </c>
       <c r="V6" t="n">
         <v>1.6083</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4591</v>
+        <v>-0.1724</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4665</v>
+        <v>-1.1127</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0075</v>
+        <v>0.9402</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9242</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3752</v>
+        <v>-0.0885</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0057</v>
       </c>
       <c r="V7" t="n">
         <v>1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.987</v>
+        <v>-0.5653</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0305</v>
+        <v>-0.4408</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0435</v>
+        <v>-0.1245</v>
       </c>
       <c r="G8" t="n">
         <v>1.4272</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3113</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8215</v>
+        <v>-0.2317</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4898</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>2.1444</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9475</v>
+        <v>-1.5632</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6583</v>
+        <v>0.3413</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6058</v>
+        <v>-1.9045</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6028</v>
+        <v>2.5728</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5292</v>
+        <v>-0.5891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0736</v>
+        <v>3.162</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7166</v>
+        <v>3.8564</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1043</v>
+        <v>-0.3627</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6122</v>
+        <v>4.2191</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3194</v>
+        <v>-1.2836</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6335</v>
+        <v>-0.2264</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6859</v>
+        <v>-1.0572</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9278</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.232</v>
+        <v>-4.871</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4116</v>
+        <v>-1.1903</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1098</v>
+        <v>0.1419</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3018</v>
+        <v>-1.3322</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8608</v>
+        <v>-0.3943</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2836</v>
+        <v>1.214</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9733</v>
+        <v>-2.1423</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4971</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4758</v>
+        <v>-2.6394</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5728</v>
+        <v>-0.6028</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5891</v>
+        <v>-0.5292</v>
       </c>
       <c r="I10" t="n">
-        <v>3.162</v>
+        <v>-0.0736</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8564</v>
+        <v>0.7166</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3627</v>
+        <v>0.1043</v>
       </c>
       <c r="L10" t="n">
-        <v>4.2191</v>
+        <v>0.6122</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2836</v>
+        <v>-1.3194</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2264</v>
+        <v>-0.6335</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0572</v>
+        <v>-0.6859</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.871</v>
+        <v>-0.232</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3195</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6004</v>
+        <v>-0.6065</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3031</v>
+        <v>-0.2711</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.9035</v>
+        <v>-0.3354</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3943</v>
+        <v>-1.8608</v>
       </c>
       <c r="W10" t="n">
-        <v>1.214</v>
+        <v>0.2836</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="11">
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.011199999999999</v>
+        <v>9.384499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>16.2718</v>
+        <v>16.6452</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.2606</v>
+        <v>-7.2607</v>
       </c>
       <c r="G11" t="n">
         <v>11.6621</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7008</v>
+        <v>-0.7007999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>12.3629</v>
@@ -1288,7 +1288,7 @@
         <v>21.7086</v>
       </c>
       <c r="K11" t="n">
-        <v>3.005999999999999</v>
+        <v>3.006</v>
       </c>
       <c r="L11" t="n">
         <v>18.7026</v>
@@ -1312,13 +1312,13 @@
         <v>12.7575</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.3447</v>
+        <v>-3.9713</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.01770000000000022</v>
+        <v>0.3558999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.327100000000001</v>
+        <v>-4.327</v>
       </c>
       <c r="V11" t="n">
         <v>2.8533</v>
@@ -1327,7 +1327,7 @@
         <v>8.4979</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.6446</v>
+        <v>-5.644600000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.757</v>
+        <v>6.8515</v>
       </c>
       <c r="E12" t="n">
-        <v>6.6788</v>
+        <v>7.5045</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9218</v>
+        <v>-0.653</v>
       </c>
       <c r="G12" t="n">
         <v>6.5726</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6017</v>
+        <v>-0.5072</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9709</v>
+        <v>-0.1452</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6308</v>
+        <v>-0.362</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0554</v>
+        <v>6.1327</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5628</v>
+        <v>5.2705</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4926</v>
+        <v>0.8623</v>
       </c>
       <c r="G13" t="n">
         <v>2.5018</v>
@@ -1468,13 +1468,13 @@
         <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2867</v>
+        <v>-0.2093</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8215</v>
+        <v>-0.1138</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4652</v>
+        <v>-0.0955</v>
       </c>
       <c r="V13" t="n">
         <v>2.6805</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7068</v>
+        <v>1.2693</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5778</v>
+        <v>1.3419</v>
       </c>
       <c r="F14" t="n">
-        <v>0.129</v>
+        <v>-0.0726</v>
       </c>
       <c r="G14" t="n">
         <v>0.6894</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3216</v>
+        <v>-0.116</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3383</v>
+        <v>0.1024</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0167</v>
+        <v>-0.2183</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1243</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4826</v>
+        <v>0.4054</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6069</v>
+        <v>-0.3257</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.332</v>
+        <v>-0.4855</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2546</v>
+        <v>0.0732</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0774</v>
+        <v>-0.5587</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2803</v>
+        <v>0.1576</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4607</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8196</v>
+        <v>0.0736</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.6123</v>
+        <v>-0.6431</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7153</v>
+        <v>-0.0108</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.897</v>
+        <v>-0.6323</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3315</v>
+        <v>0.1013</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8259</v>
+        <v>0.2478</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5056</v>
+        <v>-0.1465</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.493</v>
+        <v>-0.6627</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0664</v>
+        <v>1.2467</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4265</v>
+        <v>-1.9093</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4855</v>
+        <v>-1.332</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0732</v>
+        <v>-0.2546</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5587</v>
+        <v>-1.0774</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1576</v>
+        <v>1.2803</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.4607</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0736</v>
+        <v>0.8196</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6431</v>
+        <v>-2.6123</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0108</v>
+        <v>-0.7153</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6323</v>
+        <v>-1.897</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4714</v>
+        <v>0.7932</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.224</v>
+        <v>0.59</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2473</v>
+        <v>0.2032</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="17">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4191</v>
+        <v>-3.1437</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1041</v>
+        <v>0.5783</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5233</v>
+        <v>-3.722</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.9463</v>
+        <v>-2.6486</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8345</v>
+        <v>-1.5981</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.1117</v>
+        <v>-1.0505</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.8567</v>
+        <v>0.8252</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4313</v>
+        <v>-0.3894</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4255</v>
+        <v>1.2146</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0895</v>
+        <v>-3.4738</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5967</v>
+        <v>-1.2087</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6862</v>
+        <v>-2.2651</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2798</v>
+        <v>0.5977</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9609</v>
+        <v>0.6293</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3189</v>
+        <v>-0.0316</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1444</v>
+        <v>-1.3247</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5592</v>
+        <v>-3.4408</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1964</v>
+        <v>-1.7831</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3628</v>
+        <v>-1.6577</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.3493</v>
+        <v>-3.9463</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8466</v>
+        <v>-0.8345</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5026</v>
+        <v>-3.1117</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4539</v>
+        <v>-2.8567</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.638</v>
+        <v>-1.4313</v>
       </c>
       <c r="L19" t="n">
-        <v>0.184</v>
+        <v>-1.4255</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.8953</v>
+        <v>-1.0895</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2087</v>
+        <v>0.5967</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.6866</v>
+        <v>-1.6862</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>4.089</v>
+        <v>1.2582</v>
       </c>
       <c r="T19" t="n">
-        <v>3.8966</v>
+        <v>1.0736</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1924</v>
+        <v>0.1845</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2836</v>
+        <v>-2.1444</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2836</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8679</v>
+        <v>-4.2357</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0115</v>
+        <v>-0.8651</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8564</v>
+        <v>-3.3705</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6486</v>
+        <v>-3.3031</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5981</v>
+        <v>-1.4192</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0505</v>
+        <v>-1.8838</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8252</v>
+        <v>1.2781</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3894</v>
+        <v>-0.8396</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2146</v>
+        <v>2.1177</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.4738</v>
+        <v>-4.5812</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2087</v>
+        <v>-0.5796</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.2651</v>
+        <v>-4.0016</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1265</v>
+        <v>0.4591</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0395</v>
+        <v>0.2638</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1661</v>
+        <v>0.1953</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3247</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2759</v>
+        <v>-4.8878</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4894</v>
+        <v>-2.8997</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7865</v>
+        <v>-1.9881</v>
       </c>
       <c r="G21" t="n">
         <v>-4.8421</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1502</v>
+        <v>0.2379</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4481</v>
+        <v>0.1417</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2978</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2836</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7355</v>
+        <v>-5.9182</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3985</v>
+        <v>-3.5554</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3369</v>
+        <v>-2.3628</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3031</v>
+        <v>-4.3493</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4192</v>
+        <v>-1.8466</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8838</v>
+        <v>-2.5026</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2781</v>
+        <v>-0.4539</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8396</v>
+        <v>-0.638</v>
       </c>
       <c r="L22" t="n">
-        <v>2.1177</v>
+        <v>0.184</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.5812</v>
+        <v>-3.8953</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5796</v>
+        <v>-1.2087</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.0016</v>
+        <v>-2.6866</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3917</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-4.639</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0407</v>
+        <v>1.73</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2696</v>
+        <v>1.5375</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2289</v>
+        <v>0.1924</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="23">
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.011100000000001</v>
+        <v>-9.011099999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>7.2607</v>
+        <v>7.260800000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-16.2717</v>
+        <v>-16.2716</v>
       </c>
       <c r="G23" t="n">
         <v>-11.6624</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7008000000000001</v>
+        <v>0.7007999999999988</v>
       </c>
       <c r="I23" t="n">
         <v>-12.3628</v>
@@ -2224,16 +2224,16 @@
         <v>10.0462</v>
       </c>
       <c r="K23" t="n">
-        <v>3.706399999999999</v>
+        <v>3.7064</v>
       </c>
       <c r="L23" t="n">
-        <v>6.339600000000001</v>
+        <v>6.3396</v>
       </c>
       <c r="M23" t="n">
         <v>-21.7085</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.005800000000001</v>
+        <v>-3.0058</v>
       </c>
       <c r="O23" t="n">
         <v>-18.7025</v>
@@ -2248,16 +2248,16 @@
         <v>13.9172</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3447</v>
+        <v>4.344900000000001</v>
       </c>
       <c r="T23" t="n">
         <v>4.3271</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01750000000000002</v>
+        <v>0.01769999999999997</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.8534</v>
+        <v>-2.853399999999999</v>
       </c>
       <c r="W23" t="n">
         <v>5.644600000000001</v>
